--- a/draftTAPPs/XANES_TAPP_draft_v2.xlsx
+++ b/draftTAPPs/XANES_TAPP_draft_v2.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,60 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000070C0"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007030A0"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00375623"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -94,62 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2002,12 +1901,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Acquisition Software</t>
+          <t>Beamline</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Instrument control, automation and data acquisition software used to collect the raw data, including version number. Distinct from Data Processing Software(s), which covers everything applied to the data after acquisition.</t>
+          <t>Identifier or name of the synchrotron beamline at which the measurement was made. Distinguished from Instrument Model, which conflates the two today: the ADA corpus records the beamline inside the model string. Classified as a NeXus NXinstrument.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2017,7 +1916,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Editable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2027,17 +1926,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>e.g., 'STXM_Control'</t>
+          <t>e.g., 'ALS STXM beamline 5.3.2.2'</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Source: Core module</t>
+          <t>Seeded 2026-10-14 from the ADA corpus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2047,129 +1946,124 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ALS STXM beamline 5.3.2.2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Acquisition Software</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Instrument control, automation and data acquisition software used to collect the raw data, including version number. Distinct from Data Processing Software(s), which covers everything applied to the data after acquisition.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>e.g., 'STXM_Control'</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Data Processing Software(s)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>All software applied to the data after acquisition in order to produce the reported quantities, including version numbers. List every package used. Distinct from Acquisition Software, which controls the instrument and collects the raw data.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>e.g., 'aXis2000' | 'MANTiS'</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>4. Measurement Information</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytical Mode</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary analytical mode(s) executed under this procedure. Records one value for a single-mode procedure and all applicable modes for a multi-mode one. Applies even where a procedure defines no mode flag columns.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Read-Only</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Controlled list</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Hyperspectral image stack</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability.</t>
+          <t>4. Measurement Information</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2181,107 +2075,117 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Analytical Mode</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Primary analytical mode(s) executed under this procedure. Records one value for a single-mode procedure and all applicable modes for a multi-mode one. Applies even where a procedure defines no mode flag columns.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Hyperspectral image stack</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Reported Variables and Units</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>The final variable(s) this procedure reports and their units — distinct from the fields recording what was *acquired* rather than what is reported. Record every reported variable, including intermediate quantities reported alongside final ones (e.g. both the 206Pb/238U ratio and the 206Pb/238U date). Where a reported variable is a nominal property with no magnitude (e.g. a mineral identification), record the variable and give the unit as 'N/A — nominal property'.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>5. Data Processing</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Calibration Factor and Determination Method</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>An externally-calibrated factor that converts the measured quantity into the reported quantity, how it was determined, and its uncertainty. Applies where the conversion depends on a factor calibrated against a reference of independently known value, rather than on the instrument response alone. Distinct from the fields that name the calibration material and that state which approach applies to which analyte, where the technique has them: this field records the resulting factor itself.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Editable</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Text (free)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Source: Calibration Factor module</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>reported property</t>
+          <t>5. Data Processing</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2293,121 +2197,168 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Calibration Factor and Determination Method</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>An externally-calibrated factor that converts the measured quantity into the reported quantity, how it was determined, and its uncertainty. Applies where the conversion depends on a factor calibrated against a reference of independently known value, rather than on the instrument response alone. Distinct from the fields that name the calibration material and that state which approach applies to which analyte, where the technique has them: this field records the resulting factor itself.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Source: Calibration Factor module</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>reported property</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Constants and Reference Values Used</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Physical constants and reference values used in data reduction to calculate the final reported quantity (e.g., decay constants for age calculation, standard isotope ratios, or other citable reference values used in a correction or calculation), together with their source. Distinct from the Group 6 reference-material fields, which document accepted values for specific calibration/validation materials rather than universal physical constants. Record "None" if no citable, revisable physical constants feed into this procedure's data reduction.</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>e.g., 'ICDD PDF-4+ 2024 reference patterns'</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>6. Quality Control &amp; Uncertainty</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>6. Quality Control &amp; Uncertainty</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Additional Notes</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Any procedure- or analysis-specific information not captured by a structured field anywhere in this TAPP — including anomalies, deviations from the registered procedure, instrument modifications, and supplementary context. Scope is the whole document, not Group 6: this is the last field of the TAPP and covers all six groups. Use sparingly; a structured field is preferred for anything that can be formally categorised.</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Source: Core module</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Source: Core module</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2421,312 +2372,311 @@
   </sheetPr>
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="75" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Procedure-Level Tier</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Analysis-Level Tier</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Mandatory for procedure registration. Must be provided to register a valid procedure.</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Directly imported from the registered procedure; cannot be changed by the analyst. Changing this value means running a different procedure. Also used for fields relevant only at procedure level — the value is inherited from the procedure record and shown read-only in the analysis form.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Optional for procedure registration. Strongly recommended but not required.</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Editable</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Imported from the registered procedure but may be adjusted within procedure-defined bounds (e.g., daily tuning, minor software updates). The procedure registers the target or typical value; the analyst confirms or adjusts it. Cannot be left void if the procedure-level tier is Basic.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Not applicable at procedure level. This field captures analysis-level information only.</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Mandatory user input at analysis time. Value comes from the analysis itself and cannot be pre-specified in the procedure.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Optional user input at analysis time. Recommended for complete and reproducible documentation.</t>
         </is>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Mode Column</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>This field applies to this analytical mode and should be reported.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>This field does not apply to this analytical mode.</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Controlled list</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Controlled list / Text</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Numeric (unit)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Numeric + unit</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Text (free)</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Free text. No controlled vocabulary applies.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>N/A | None</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Keyed By (Rule 7)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>What the field's value repeats over</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Scalar — one value per procedure or analysis. The default.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>defines: sample</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>defines: sampling unit</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>reported property</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
